--- a/PTBR/Lang/PTBR/Dialog/Drama/casino_clerk.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/casino_clerk.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esta é sua primeira visita hoje, certo? Aqui está sua raspadinha grátis! </t>
+          <t xml:space="preserve">Esta é a sua primeira visita hoje, né? Aqui está seu cartão de raspadinha grátis! </t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>O sino dourado anuncia a boa sorte... Bem-vindo ao ''Sino da Fortuna'', o único dirigível de cassino do mundo. Sinta-se à vontade para aproveitar até que sua carteira esteja vazia.</t>
+          <t>O sino dourado anuncia boa fortuna... Bem-vindo ao 'Sino da Fortuna', a única aeronave-cassino do mundo. Aproveite à vontade, até sua carteira esvaziar.</t>
         </is>
       </c>
     </row>
